--- a/ExcelFiles/FFmpeg.xlsx
+++ b/ExcelFiles/FFmpeg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/muyeedahmed/Desktop/Gitcode/LLMVerification/ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428A9146-6CC9-244A-A984-24C6DE53C92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151C7979-DC41-BC42-98C4-B09B7181564A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1360" yWindow="500" windowWidth="27440" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41480" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Commits" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="316">
   <si>
     <t>Commit Date</t>
   </si>
@@ -1059,6 +1059,12 @@
   </si>
   <si>
     <t>Deleted Code</t>
+  </si>
+  <si>
+    <t>No Change/Empty</t>
+  </si>
+  <si>
+    <t>Output Incorrect Function</t>
   </si>
 </sst>
 </file>
@@ -1578,7 +1584,7 @@
         <v>212</v>
       </c>
       <c r="K3" t="s">
-        <v>212</v>
+        <v>315</v>
       </c>
       <c r="L3" t="s">
         <v>216</v>
@@ -1889,7 +1895,7 @@
         <v>212</v>
       </c>
       <c r="K10" t="s">
-        <v>212</v>
+        <v>315</v>
       </c>
       <c r="L10" t="s">
         <v>218</v>
@@ -2077,7 +2083,7 @@
         <v>212</v>
       </c>
       <c r="K14" t="s">
-        <v>214</v>
+        <v>313</v>
       </c>
       <c r="L14" t="s">
         <v>216</v>
@@ -2124,7 +2130,7 @@
         <v>214</v>
       </c>
       <c r="K15" t="s">
-        <v>212</v>
+        <v>315</v>
       </c>
       <c r="L15" t="s">
         <v>216</v>
@@ -2259,7 +2265,7 @@
         <v>246</v>
       </c>
       <c r="K18" t="s">
-        <v>212</v>
+        <v>310</v>
       </c>
       <c r="L18" t="s">
         <v>216</v>
@@ -2401,7 +2407,7 @@
         <v>212</v>
       </c>
       <c r="K21" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="L21" t="s">
         <v>216</v>
@@ -2589,7 +2595,7 @@
         <v>212</v>
       </c>
       <c r="K25" t="s">
-        <v>212</v>
+        <v>315</v>
       </c>
       <c r="L25" t="s">
         <v>218</v>
@@ -2639,7 +2645,7 @@
         <v>212</v>
       </c>
       <c r="K26" t="s">
-        <v>212</v>
+        <v>315</v>
       </c>
       <c r="L26" t="s">
         <v>218</v>
@@ -2686,7 +2692,7 @@
         <v>213</v>
       </c>
       <c r="K27" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="L27" t="s">
         <v>216</v>
@@ -2865,7 +2871,7 @@
         <v>214</v>
       </c>
       <c r="K31" t="s">
-        <v>212</v>
+        <v>315</v>
       </c>
       <c r="L31" t="s">
         <v>216</v>
@@ -2912,6 +2918,9 @@
       <c r="I32" t="s">
         <v>212</v>
       </c>
+      <c r="K32" t="s">
+        <v>315</v>
+      </c>
       <c r="L32" t="s">
         <v>291</v>
       </c>
@@ -2956,6 +2965,9 @@
       <c r="I33" t="s">
         <v>255</v>
       </c>
+      <c r="K33" t="s">
+        <v>255</v>
+      </c>
       <c r="L33" t="s">
         <v>256</v>
       </c>
@@ -3000,6 +3012,9 @@
       <c r="I34" t="s">
         <v>211</v>
       </c>
+      <c r="K34" t="s">
+        <v>315</v>
+      </c>
       <c r="L34" t="s">
         <v>216</v>
       </c>
@@ -3044,6 +3059,9 @@
       <c r="I35" t="s">
         <v>212</v>
       </c>
+      <c r="K35" t="s">
+        <v>310</v>
+      </c>
       <c r="L35" t="s">
         <v>219</v>
       </c>
@@ -3088,6 +3106,9 @@
       <c r="I36" t="s">
         <v>212</v>
       </c>
+      <c r="K36" t="s">
+        <v>212</v>
+      </c>
       <c r="L36" t="s">
         <v>218</v>
       </c>
@@ -3132,6 +3153,9 @@
       <c r="I37" t="s">
         <v>212</v>
       </c>
+      <c r="K37" t="s">
+        <v>212</v>
+      </c>
       <c r="L37" t="s">
         <v>219</v>
       </c>
@@ -3176,6 +3200,9 @@
       <c r="I38" t="s">
         <v>212</v>
       </c>
+      <c r="K38" t="s">
+        <v>212</v>
+      </c>
       <c r="L38" t="s">
         <v>256</v>
       </c>
@@ -3220,6 +3247,9 @@
       <c r="I39" t="s">
         <v>212</v>
       </c>
+      <c r="K39" t="s">
+        <v>212</v>
+      </c>
       <c r="L39" t="s">
         <v>219</v>
       </c>
@@ -3264,6 +3294,9 @@
       <c r="I40" t="s">
         <v>213</v>
       </c>
+      <c r="K40" t="s">
+        <v>212</v>
+      </c>
       <c r="L40" t="s">
         <v>219</v>
       </c>
@@ -3296,6 +3329,9 @@
       <c r="I41" t="s">
         <v>255</v>
       </c>
+      <c r="K41" t="s">
+        <v>214</v>
+      </c>
       <c r="L41" t="s">
         <v>218</v>
       </c>
@@ -3340,6 +3376,9 @@
       <c r="I42" t="s">
         <v>255</v>
       </c>
+      <c r="K42" t="s">
+        <v>310</v>
+      </c>
       <c r="L42" t="s">
         <v>216</v>
       </c>
@@ -3384,6 +3423,9 @@
       <c r="I43" t="s">
         <v>212</v>
       </c>
+      <c r="K43" t="s">
+        <v>315</v>
+      </c>
       <c r="L43" t="s">
         <v>216</v>
       </c>
@@ -3428,6 +3470,9 @@
       <c r="I44" t="s">
         <v>214</v>
       </c>
+      <c r="K44" t="s">
+        <v>212</v>
+      </c>
       <c r="L44" t="s">
         <v>216</v>
       </c>
@@ -3460,6 +3505,9 @@
       <c r="I45" t="s">
         <v>246</v>
       </c>
+      <c r="K45" t="s">
+        <v>212</v>
+      </c>
       <c r="L45" t="s">
         <v>216</v>
       </c>
@@ -3504,6 +3552,9 @@
       <c r="I46" t="s">
         <v>214</v>
       </c>
+      <c r="K46" t="s">
+        <v>310</v>
+      </c>
       <c r="L46" t="s">
         <v>216</v>
       </c>
@@ -3548,6 +3599,9 @@
       <c r="I47" t="s">
         <v>212</v>
       </c>
+      <c r="K47" t="s">
+        <v>315</v>
+      </c>
       <c r="L47" t="s">
         <v>216</v>
       </c>
@@ -3593,6 +3647,9 @@
       <c r="I48" t="s">
         <v>235</v>
       </c>
+      <c r="K48" t="s">
+        <v>315</v>
+      </c>
       <c r="L48" t="s">
         <v>219</v>
       </c>
@@ -3637,6 +3694,9 @@
       <c r="I49" t="s">
         <v>212</v>
       </c>
+      <c r="K49" t="s">
+        <v>315</v>
+      </c>
       <c r="L49" t="s">
         <v>220</v>
       </c>
@@ -3681,6 +3741,9 @@
       <c r="I50" t="s">
         <v>215</v>
       </c>
+      <c r="K50" t="s">
+        <v>310</v>
+      </c>
       <c r="L50" t="s">
         <v>216</v>
       </c>
@@ -3713,6 +3776,9 @@
       <c r="I51" t="s">
         <v>213</v>
       </c>
+      <c r="K51" t="s">
+        <v>315</v>
+      </c>
       <c r="L51" t="s">
         <v>216</v>
       </c>
@@ -3757,6 +3823,9 @@
       <c r="I52" t="s">
         <v>212</v>
       </c>
+      <c r="K52" t="s">
+        <v>212</v>
+      </c>
       <c r="L52" t="s">
         <v>217</v>
       </c>
@@ -3804,6 +3873,9 @@
       <c r="I53" t="s">
         <v>214</v>
       </c>
+      <c r="K53" t="s">
+        <v>212</v>
+      </c>
       <c r="L53" t="s">
         <v>219</v>
       </c>
@@ -3848,6 +3920,9 @@
       <c r="I54" t="s">
         <v>212</v>
       </c>
+      <c r="K54" t="s">
+        <v>310</v>
+      </c>
       <c r="L54" t="s">
         <v>256</v>
       </c>
@@ -3892,6 +3967,9 @@
       <c r="I55" t="s">
         <v>212</v>
       </c>
+      <c r="K55" t="s">
+        <v>315</v>
+      </c>
       <c r="L55" t="s">
         <v>218</v>
       </c>
@@ -3936,6 +4014,9 @@
       <c r="I56" t="s">
         <v>214</v>
       </c>
+      <c r="K56" t="s">
+        <v>213</v>
+      </c>
       <c r="L56" t="s">
         <v>216</v>
       </c>
@@ -3980,6 +4061,9 @@
       <c r="I57" t="s">
         <v>214</v>
       </c>
+      <c r="K57" t="s">
+        <v>214</v>
+      </c>
       <c r="L57" t="s">
         <v>216</v>
       </c>
@@ -4024,6 +4108,9 @@
       <c r="I58" t="s">
         <v>213</v>
       </c>
+      <c r="K58" t="s">
+        <v>213</v>
+      </c>
       <c r="L58" t="s">
         <v>220</v>
       </c>
@@ -4068,6 +4155,9 @@
       <c r="I59" t="s">
         <v>213</v>
       </c>
+      <c r="K59" t="s">
+        <v>213</v>
+      </c>
       <c r="L59" t="s">
         <v>216</v>
       </c>
@@ -4100,6 +4190,9 @@
       <c r="I60" t="s">
         <v>235</v>
       </c>
+      <c r="K60" t="s">
+        <v>315</v>
+      </c>
       <c r="L60" t="s">
         <v>216</v>
       </c>
@@ -4144,6 +4237,9 @@
       <c r="I61" t="s">
         <v>212</v>
       </c>
+      <c r="K61" t="s">
+        <v>315</v>
+      </c>
       <c r="L61" t="s">
         <v>216</v>
       </c>
@@ -4188,6 +4284,9 @@
       <c r="I62" t="s">
         <v>212</v>
       </c>
+      <c r="K62" t="s">
+        <v>310</v>
+      </c>
       <c r="L62" t="s">
         <v>216</v>
       </c>
@@ -4232,6 +4331,9 @@
       <c r="I63" t="s">
         <v>215</v>
       </c>
+      <c r="K63" t="s">
+        <v>315</v>
+      </c>
       <c r="L63" t="s">
         <v>216</v>
       </c>
@@ -4276,6 +4378,12 @@
       <c r="I64" t="s">
         <v>214</v>
       </c>
+      <c r="J64" t="s">
+        <v>314</v>
+      </c>
+      <c r="K64" t="s">
+        <v>310</v>
+      </c>
       <c r="L64" t="s">
         <v>216</v>
       </c>
@@ -4308,6 +4416,9 @@
       <c r="I65" t="s">
         <v>280</v>
       </c>
+      <c r="K65" t="s">
+        <v>315</v>
+      </c>
       <c r="L65" t="s">
         <v>216</v>
       </c>
@@ -4352,6 +4463,9 @@
       <c r="I66" t="s">
         <v>212</v>
       </c>
+      <c r="K66" t="s">
+        <v>315</v>
+      </c>
       <c r="L66" t="s">
         <v>216</v>
       </c>
@@ -4396,6 +4510,9 @@
       <c r="I67" t="s">
         <v>212</v>
       </c>
+      <c r="K67" t="s">
+        <v>212</v>
+      </c>
       <c r="L67" t="s">
         <v>218</v>
       </c>
@@ -4440,6 +4557,9 @@
       <c r="I68" t="s">
         <v>255</v>
       </c>
+      <c r="K68" t="s">
+        <v>315</v>
+      </c>
       <c r="L68" t="s">
         <v>218</v>
       </c>
@@ -4484,6 +4604,9 @@
       <c r="I69" t="s">
         <v>212</v>
       </c>
+      <c r="K69" t="s">
+        <v>212</v>
+      </c>
       <c r="L69" t="s">
         <v>220</v>
       </c>
@@ -4529,6 +4652,9 @@
       <c r="I70" t="s">
         <v>214</v>
       </c>
+      <c r="K70" t="s">
+        <v>214</v>
+      </c>
       <c r="L70" t="s">
         <v>291</v>
       </c>
@@ -4573,6 +4699,9 @@
       <c r="I71" t="s">
         <v>212</v>
       </c>
+      <c r="K71" t="s">
+        <v>315</v>
+      </c>
       <c r="L71" t="s">
         <v>219</v>
       </c>
@@ -4617,6 +4746,9 @@
       <c r="I72" t="s">
         <v>212</v>
       </c>
+      <c r="K72" t="s">
+        <v>315</v>
+      </c>
       <c r="L72" t="s">
         <v>219</v>
       </c>
@@ -4661,6 +4793,9 @@
       <c r="I73" t="s">
         <v>212</v>
       </c>
+      <c r="K73" t="s">
+        <v>315</v>
+      </c>
       <c r="L73" t="s">
         <v>220</v>
       </c>
@@ -4705,6 +4840,9 @@
       <c r="I74" t="s">
         <v>255</v>
       </c>
+      <c r="K74" t="s">
+        <v>315</v>
+      </c>
       <c r="L74" t="s">
         <v>218</v>
       </c>
@@ -4749,6 +4887,9 @@
       <c r="I75" t="s">
         <v>212</v>
       </c>
+      <c r="K75" t="s">
+        <v>213</v>
+      </c>
       <c r="L75" t="s">
         <v>216</v>
       </c>
@@ -4780,6 +4921,9 @@
       </c>
       <c r="I76" t="s">
         <v>255</v>
+      </c>
+      <c r="K76" t="s">
+        <v>212</v>
       </c>
       <c r="L76" t="s">
         <v>220</v>

--- a/ExcelFiles/FFmpeg.xlsx
+++ b/ExcelFiles/FFmpeg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/muyeedahmed/Desktop/Gitcode/LLMVerification/ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151C7979-DC41-BC42-98C4-B09B7181564A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1897CD70-329B-F34A-9B8F-D69B497993EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="41480" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ExcelFiles/FFmpeg.xlsx
+++ b/ExcelFiles/FFmpeg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/muyeedahmed/Desktop/Gitcode/LLMVerification/ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1897CD70-329B-F34A-9B8F-D69B497993EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6F7BD5-B53A-7C4A-A8B2-C0793470D630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="41480" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="316">
   <si>
     <t>Commit Date</t>
   </si>
@@ -1061,10 +1061,10 @@
     <t>Deleted Code</t>
   </si>
   <si>
-    <t>No Change/Empty</t>
-  </si>
-  <si>
     <t>Output Incorrect Function</t>
+  </si>
+  <si>
+    <t>Incomplete File</t>
   </si>
 </sst>
 </file>
@@ -1448,14 +1448,14 @@
   <dimension ref="A1:R76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.5" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="3" max="3" width="0.6640625" customWidth="1"/>
+    <col min="4" max="4" width="1.1640625" customWidth="1"/>
+    <col min="5" max="5" width="41.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3.83203125" customWidth="1"/>
     <col min="7" max="8" width="4.1640625" customWidth="1"/>
-    <col min="9" max="9" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22" bestFit="1" customWidth="1"/>
@@ -1583,8 +1583,11 @@
       <c r="I3" t="s">
         <v>212</v>
       </c>
+      <c r="J3" t="s">
+        <v>315</v>
+      </c>
       <c r="K3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L3" t="s">
         <v>216</v>
@@ -1895,7 +1898,7 @@
         <v>212</v>
       </c>
       <c r="K10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L10" t="s">
         <v>218</v>
@@ -2130,7 +2133,7 @@
         <v>214</v>
       </c>
       <c r="K15" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L15" t="s">
         <v>216</v>
@@ -2264,6 +2267,9 @@
       <c r="I18" t="s">
         <v>246</v>
       </c>
+      <c r="J18" t="s">
+        <v>315</v>
+      </c>
       <c r="K18" t="s">
         <v>310</v>
       </c>
@@ -2311,6 +2317,9 @@
       <c r="I19" t="s">
         <v>212</v>
       </c>
+      <c r="J19" t="s">
+        <v>315</v>
+      </c>
       <c r="K19" t="s">
         <v>310</v>
       </c>
@@ -2406,8 +2415,11 @@
       <c r="I21" t="s">
         <v>212</v>
       </c>
+      <c r="J21" t="s">
+        <v>315</v>
+      </c>
       <c r="K21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L21" t="s">
         <v>216</v>
@@ -2595,7 +2607,7 @@
         <v>212</v>
       </c>
       <c r="K25" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L25" t="s">
         <v>218</v>
@@ -2645,7 +2657,7 @@
         <v>212</v>
       </c>
       <c r="K26" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L26" t="s">
         <v>218</v>
@@ -2692,7 +2704,7 @@
         <v>213</v>
       </c>
       <c r="K27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L27" t="s">
         <v>216</v>
@@ -2870,8 +2882,11 @@
       <c r="I31" t="s">
         <v>214</v>
       </c>
+      <c r="J31" t="s">
+        <v>315</v>
+      </c>
       <c r="K31" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L31" t="s">
         <v>216</v>
@@ -2918,8 +2933,11 @@
       <c r="I32" t="s">
         <v>212</v>
       </c>
+      <c r="J32" t="s">
+        <v>315</v>
+      </c>
       <c r="K32" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L32" t="s">
         <v>291</v>
@@ -3013,7 +3031,7 @@
         <v>211</v>
       </c>
       <c r="K34" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L34" t="s">
         <v>216</v>
@@ -3200,6 +3218,9 @@
       <c r="I38" t="s">
         <v>212</v>
       </c>
+      <c r="J38" t="s">
+        <v>315</v>
+      </c>
       <c r="K38" t="s">
         <v>212</v>
       </c>
@@ -3423,8 +3444,11 @@
       <c r="I43" t="s">
         <v>212</v>
       </c>
+      <c r="J43" t="s">
+        <v>312</v>
+      </c>
       <c r="K43" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L43" t="s">
         <v>216</v>
@@ -3470,6 +3494,9 @@
       <c r="I44" t="s">
         <v>214</v>
       </c>
+      <c r="J44" t="s">
+        <v>315</v>
+      </c>
       <c r="K44" t="s">
         <v>212</v>
       </c>
@@ -3552,6 +3579,9 @@
       <c r="I46" t="s">
         <v>214</v>
       </c>
+      <c r="J46" t="s">
+        <v>315</v>
+      </c>
       <c r="K46" t="s">
         <v>310</v>
       </c>
@@ -3599,8 +3629,11 @@
       <c r="I47" t="s">
         <v>212</v>
       </c>
+      <c r="J47" t="s">
+        <v>315</v>
+      </c>
       <c r="K47" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L47" t="s">
         <v>216</v>
@@ -3647,8 +3680,11 @@
       <c r="I48" t="s">
         <v>235</v>
       </c>
+      <c r="J48" t="s">
+        <v>315</v>
+      </c>
       <c r="K48" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L48" t="s">
         <v>219</v>
@@ -3694,8 +3730,11 @@
       <c r="I49" t="s">
         <v>212</v>
       </c>
+      <c r="J49" t="s">
+        <v>312</v>
+      </c>
       <c r="K49" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L49" t="s">
         <v>220</v>
@@ -3777,7 +3816,7 @@
         <v>213</v>
       </c>
       <c r="K51" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L51" t="s">
         <v>216</v>
@@ -3967,8 +4006,11 @@
       <c r="I55" t="s">
         <v>212</v>
       </c>
+      <c r="J55" t="s">
+        <v>315</v>
+      </c>
       <c r="K55" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L55" t="s">
         <v>218</v>
@@ -4190,8 +4232,11 @@
       <c r="I60" t="s">
         <v>235</v>
       </c>
+      <c r="J60" t="s">
+        <v>315</v>
+      </c>
       <c r="K60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L60" t="s">
         <v>216</v>
@@ -4238,7 +4283,7 @@
         <v>212</v>
       </c>
       <c r="K61" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L61" t="s">
         <v>216</v>
@@ -4332,7 +4377,7 @@
         <v>215</v>
       </c>
       <c r="K63" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L63" t="s">
         <v>216</v>
@@ -4379,7 +4424,7 @@
         <v>214</v>
       </c>
       <c r="J64" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K64" t="s">
         <v>310</v>
@@ -4416,8 +4461,11 @@
       <c r="I65" t="s">
         <v>280</v>
       </c>
+      <c r="J65" t="s">
+        <v>315</v>
+      </c>
       <c r="K65" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L65" t="s">
         <v>216</v>
@@ -4463,8 +4511,11 @@
       <c r="I66" t="s">
         <v>212</v>
       </c>
+      <c r="J66" t="s">
+        <v>315</v>
+      </c>
       <c r="K66" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L66" t="s">
         <v>216</v>
@@ -4558,7 +4609,7 @@
         <v>255</v>
       </c>
       <c r="K68" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L68" t="s">
         <v>218</v>
@@ -4604,6 +4655,9 @@
       <c r="I69" t="s">
         <v>212</v>
       </c>
+      <c r="J69" t="s">
+        <v>315</v>
+      </c>
       <c r="K69" t="s">
         <v>212</v>
       </c>
@@ -4700,7 +4754,7 @@
         <v>212</v>
       </c>
       <c r="K71" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L71" t="s">
         <v>219</v>
@@ -4746,8 +4800,11 @@
       <c r="I72" t="s">
         <v>212</v>
       </c>
+      <c r="J72" t="s">
+        <v>315</v>
+      </c>
       <c r="K72" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L72" t="s">
         <v>219</v>
@@ -4793,8 +4850,11 @@
       <c r="I73" t="s">
         <v>212</v>
       </c>
+      <c r="J73" t="s">
+        <v>315</v>
+      </c>
       <c r="K73" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L73" t="s">
         <v>220</v>
@@ -4840,8 +4900,11 @@
       <c r="I74" t="s">
         <v>255</v>
       </c>
+      <c r="J74" t="s">
+        <v>312</v>
+      </c>
       <c r="K74" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L74" t="s">
         <v>218</v>
@@ -4887,6 +4950,9 @@
       <c r="I75" t="s">
         <v>212</v>
       </c>
+      <c r="J75" t="s">
+        <v>315</v>
+      </c>
       <c r="K75" t="s">
         <v>213</v>
       </c>
@@ -4921,6 +4987,9 @@
       </c>
       <c r="I76" t="s">
         <v>255</v>
+      </c>
+      <c r="J76" t="s">
+        <v>315</v>
       </c>
       <c r="K76" t="s">
         <v>212</v>

--- a/ExcelFiles/FFmpeg.xlsx
+++ b/ExcelFiles/FFmpeg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/muyeedahmed/Desktop/Gitcode/LLMVerification/ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6F7BD5-B53A-7C4A-A8B2-C0793470D630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76256CB7-724E-3B4F-BE97-099A96805E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41480" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1420" yWindow="500" windowWidth="27380" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Commits" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="316">
   <si>
     <t>Commit Date</t>
   </si>
@@ -1633,6 +1633,9 @@
       <c r="I4" t="s">
         <v>212</v>
       </c>
+      <c r="J4" t="s">
+        <v>213</v>
+      </c>
       <c r="K4" t="s">
         <v>212</v>
       </c>
@@ -1668,6 +1671,9 @@
       <c r="I5" t="s">
         <v>213</v>
       </c>
+      <c r="J5" t="s">
+        <v>310</v>
+      </c>
       <c r="K5" t="s">
         <v>212</v>
       </c>
@@ -1715,6 +1721,9 @@
       <c r="I6" t="s">
         <v>235</v>
       </c>
+      <c r="J6" t="s">
+        <v>310</v>
+      </c>
       <c r="K6" t="s">
         <v>212</v>
       </c>
@@ -1762,6 +1771,9 @@
       <c r="I7" t="s">
         <v>212</v>
       </c>
+      <c r="J7" t="s">
+        <v>212</v>
+      </c>
       <c r="K7" t="s">
         <v>212</v>
       </c>
@@ -1815,6 +1827,9 @@
       <c r="I8" t="s">
         <v>212</v>
       </c>
+      <c r="J8" t="s">
+        <v>310</v>
+      </c>
       <c r="K8" t="s">
         <v>310</v>
       </c>
@@ -1862,6 +1877,9 @@
       <c r="I9" t="s">
         <v>214</v>
       </c>
+      <c r="J9" t="s">
+        <v>213</v>
+      </c>
       <c r="K9" t="s">
         <v>212</v>
       </c>
@@ -1897,6 +1915,9 @@
       <c r="I10" t="s">
         <v>212</v>
       </c>
+      <c r="J10" t="s">
+        <v>212</v>
+      </c>
       <c r="K10" t="s">
         <v>314</v>
       </c>
@@ -1944,6 +1965,9 @@
       <c r="I11" t="s">
         <v>212</v>
       </c>
+      <c r="J11" t="s">
+        <v>212</v>
+      </c>
       <c r="K11" t="s">
         <v>212</v>
       </c>
@@ -1991,6 +2015,9 @@
       <c r="I12" t="s">
         <v>213</v>
       </c>
+      <c r="J12" t="s">
+        <v>214</v>
+      </c>
       <c r="K12" t="s">
         <v>212</v>
       </c>
@@ -2038,6 +2065,9 @@
       <c r="I13" t="s">
         <v>212</v>
       </c>
+      <c r="J13" t="s">
+        <v>310</v>
+      </c>
       <c r="K13" t="s">
         <v>212</v>
       </c>
@@ -2085,6 +2115,9 @@
       <c r="I14" t="s">
         <v>212</v>
       </c>
+      <c r="J14" t="s">
+        <v>213</v>
+      </c>
       <c r="K14" t="s">
         <v>313</v>
       </c>
@@ -2132,6 +2165,9 @@
       <c r="I15" t="s">
         <v>214</v>
       </c>
+      <c r="J15" t="s">
+        <v>315</v>
+      </c>
       <c r="K15" t="s">
         <v>314</v>
       </c>
@@ -2179,6 +2215,9 @@
       <c r="I16" t="s">
         <v>212</v>
       </c>
+      <c r="J16" t="s">
+        <v>212</v>
+      </c>
       <c r="K16" t="s">
         <v>212</v>
       </c>
@@ -2220,6 +2259,9 @@
       <c r="I17" t="s">
         <v>212</v>
       </c>
+      <c r="J17" t="s">
+        <v>212</v>
+      </c>
       <c r="K17" t="s">
         <v>212</v>
       </c>
@@ -2368,6 +2410,9 @@
       <c r="I20" t="s">
         <v>212</v>
       </c>
+      <c r="J20" t="s">
+        <v>255</v>
+      </c>
       <c r="K20" t="s">
         <v>313</v>
       </c>
@@ -2465,6 +2510,9 @@
       <c r="I22" t="s">
         <v>213</v>
       </c>
+      <c r="J22" t="s">
+        <v>212</v>
+      </c>
       <c r="K22" t="s">
         <v>212</v>
       </c>
@@ -2512,6 +2560,9 @@
       <c r="I23" t="s">
         <v>213</v>
       </c>
+      <c r="J23" t="s">
+        <v>310</v>
+      </c>
       <c r="K23" t="s">
         <v>214</v>
       </c>
@@ -2559,6 +2610,9 @@
       <c r="I24" t="s">
         <v>211</v>
       </c>
+      <c r="J24" t="s">
+        <v>212</v>
+      </c>
       <c r="K24" t="s">
         <v>212</v>
       </c>
@@ -2606,6 +2660,9 @@
       <c r="I25" t="s">
         <v>212</v>
       </c>
+      <c r="J25" t="s">
+        <v>310</v>
+      </c>
       <c r="K25" t="s">
         <v>314</v>
       </c>
@@ -2654,7 +2711,7 @@
         <v>255</v>
       </c>
       <c r="J26" t="s">
-        <v>212</v>
+        <v>310</v>
       </c>
       <c r="K26" t="s">
         <v>314</v>
@@ -2703,6 +2760,9 @@
       <c r="I27" t="s">
         <v>213</v>
       </c>
+      <c r="J27" t="s">
+        <v>212</v>
+      </c>
       <c r="K27" t="s">
         <v>314</v>
       </c>
@@ -2750,6 +2810,9 @@
       <c r="I28" t="s">
         <v>212</v>
       </c>
+      <c r="J28" t="s">
+        <v>310</v>
+      </c>
       <c r="K28" t="s">
         <v>310</v>
       </c>
@@ -2797,6 +2860,9 @@
       <c r="I29" t="s">
         <v>212</v>
       </c>
+      <c r="J29" t="s">
+        <v>310</v>
+      </c>
       <c r="K29" t="s">
         <v>212</v>
       </c>
@@ -2844,6 +2910,9 @@
       <c r="I30" t="s">
         <v>212</v>
       </c>
+      <c r="J30" t="s">
+        <v>213</v>
+      </c>
       <c r="K30" t="s">
         <v>213</v>
       </c>
@@ -2983,6 +3052,9 @@
       <c r="I33" t="s">
         <v>255</v>
       </c>
+      <c r="J33" t="s">
+        <v>255</v>
+      </c>
       <c r="K33" t="s">
         <v>255</v>
       </c>
@@ -3030,6 +3102,9 @@
       <c r="I34" t="s">
         <v>211</v>
       </c>
+      <c r="J34" t="s">
+        <v>310</v>
+      </c>
       <c r="K34" t="s">
         <v>314</v>
       </c>
@@ -3077,6 +3152,9 @@
       <c r="I35" t="s">
         <v>212</v>
       </c>
+      <c r="J35" t="s">
+        <v>214</v>
+      </c>
       <c r="K35" t="s">
         <v>310</v>
       </c>
@@ -3124,6 +3202,9 @@
       <c r="I36" t="s">
         <v>212</v>
       </c>
+      <c r="J36" t="s">
+        <v>310</v>
+      </c>
       <c r="K36" t="s">
         <v>212</v>
       </c>
@@ -3171,6 +3252,9 @@
       <c r="I37" t="s">
         <v>212</v>
       </c>
+      <c r="J37" t="s">
+        <v>214</v>
+      </c>
       <c r="K37" t="s">
         <v>212</v>
       </c>
@@ -3268,6 +3352,9 @@
       <c r="I39" t="s">
         <v>212</v>
       </c>
+      <c r="J39" t="s">
+        <v>255</v>
+      </c>
       <c r="K39" t="s">
         <v>212</v>
       </c>
@@ -3315,6 +3402,9 @@
       <c r="I40" t="s">
         <v>213</v>
       </c>
+      <c r="J40" t="s">
+        <v>214</v>
+      </c>
       <c r="K40" t="s">
         <v>212</v>
       </c>
@@ -3350,6 +3440,9 @@
       <c r="I41" t="s">
         <v>255</v>
       </c>
+      <c r="J41" t="s">
+        <v>214</v>
+      </c>
       <c r="K41" t="s">
         <v>214</v>
       </c>
@@ -3397,6 +3490,9 @@
       <c r="I42" t="s">
         <v>255</v>
       </c>
+      <c r="J42" t="s">
+        <v>310</v>
+      </c>
       <c r="K42" t="s">
         <v>310</v>
       </c>
@@ -3532,6 +3628,9 @@
       <c r="I45" t="s">
         <v>246</v>
       </c>
+      <c r="J45" t="s">
+        <v>212</v>
+      </c>
       <c r="K45" t="s">
         <v>212</v>
       </c>
@@ -3780,6 +3879,9 @@
       <c r="I50" t="s">
         <v>215</v>
       </c>
+      <c r="J50" t="s">
+        <v>310</v>
+      </c>
       <c r="K50" t="s">
         <v>310</v>
       </c>
@@ -3815,6 +3917,9 @@
       <c r="I51" t="s">
         <v>213</v>
       </c>
+      <c r="J51" t="s">
+        <v>310</v>
+      </c>
       <c r="K51" t="s">
         <v>314</v>
       </c>
@@ -3862,6 +3967,9 @@
       <c r="I52" t="s">
         <v>212</v>
       </c>
+      <c r="J52" t="s">
+        <v>212</v>
+      </c>
       <c r="K52" t="s">
         <v>212</v>
       </c>
@@ -3912,6 +4020,9 @@
       <c r="I53" t="s">
         <v>214</v>
       </c>
+      <c r="J53" t="s">
+        <v>214</v>
+      </c>
       <c r="K53" t="s">
         <v>212</v>
       </c>
@@ -3959,6 +4070,9 @@
       <c r="I54" t="s">
         <v>212</v>
       </c>
+      <c r="J54" t="s">
+        <v>310</v>
+      </c>
       <c r="K54" t="s">
         <v>310</v>
       </c>
@@ -4056,6 +4170,9 @@
       <c r="I56" t="s">
         <v>214</v>
       </c>
+      <c r="J56" t="s">
+        <v>310</v>
+      </c>
       <c r="K56" t="s">
         <v>213</v>
       </c>
@@ -4103,6 +4220,9 @@
       <c r="I57" t="s">
         <v>214</v>
       </c>
+      <c r="J57" t="s">
+        <v>214</v>
+      </c>
       <c r="K57" t="s">
         <v>214</v>
       </c>
@@ -4150,6 +4270,9 @@
       <c r="I58" t="s">
         <v>213</v>
       </c>
+      <c r="J58" t="s">
+        <v>213</v>
+      </c>
       <c r="K58" t="s">
         <v>213</v>
       </c>
@@ -4197,6 +4320,9 @@
       <c r="I59" t="s">
         <v>213</v>
       </c>
+      <c r="J59" t="s">
+        <v>214</v>
+      </c>
       <c r="K59" t="s">
         <v>213</v>
       </c>
@@ -4282,6 +4408,9 @@
       <c r="I61" t="s">
         <v>212</v>
       </c>
+      <c r="J61" t="s">
+        <v>212</v>
+      </c>
       <c r="K61" t="s">
         <v>314</v>
       </c>
@@ -4329,6 +4458,9 @@
       <c r="I62" t="s">
         <v>212</v>
       </c>
+      <c r="J62" t="s">
+        <v>213</v>
+      </c>
       <c r="K62" t="s">
         <v>310</v>
       </c>
@@ -4376,6 +4508,9 @@
       <c r="I63" t="s">
         <v>215</v>
       </c>
+      <c r="J63" t="s">
+        <v>310</v>
+      </c>
       <c r="K63" t="s">
         <v>314</v>
       </c>
@@ -4561,6 +4696,9 @@
       <c r="I67" t="s">
         <v>212</v>
       </c>
+      <c r="J67" t="s">
+        <v>213</v>
+      </c>
       <c r="K67" t="s">
         <v>212</v>
       </c>
@@ -4608,6 +4746,9 @@
       <c r="I68" t="s">
         <v>255</v>
       </c>
+      <c r="J68" t="s">
+        <v>212</v>
+      </c>
       <c r="K68" t="s">
         <v>314</v>
       </c>
@@ -4706,6 +4847,9 @@
       <c r="I70" t="s">
         <v>214</v>
       </c>
+      <c r="J70" t="s">
+        <v>214</v>
+      </c>
       <c r="K70" t="s">
         <v>214</v>
       </c>
@@ -4751,6 +4895,9 @@
         <v>1</v>
       </c>
       <c r="I71" t="s">
+        <v>212</v>
+      </c>
+      <c r="J71" t="s">
         <v>212</v>
       </c>
       <c r="K71" t="s">

--- a/ExcelFiles/FFmpeg.xlsx
+++ b/ExcelFiles/FFmpeg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/muyeedahmed/Desktop/Gitcode/LLMVerification/ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76256CB7-724E-3B4F-BE97-099A96805E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4947301-10F4-4245-B106-027736B47791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1420" yWindow="500" windowWidth="27380" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ExcelFiles/FFmpeg.xlsx
+++ b/ExcelFiles/FFmpeg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/muyeedahmed/Desktop/Gitcode/LLMVerification/ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4947301-10F4-4245-B106-027736B47791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAEFC15-1F48-6147-A4F9-2C802070A8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1420" yWindow="500" windowWidth="27380" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="320">
   <si>
     <t>Commit Date</t>
   </si>
@@ -1066,6 +1066,18 @@
   <si>
     <t>Incomplete File</t>
   </si>
+  <si>
+    <t>Identical</t>
+  </si>
+  <si>
+    <t>TS_Ministral</t>
+  </si>
+  <si>
+    <t>TS_Qwen3</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
 </sst>
 </file>
 
@@ -1091,12 +1103,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1126,7 +1150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1141,6 +1165,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1445,23 +1472,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R76"/>
+  <dimension ref="A1:T76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" customWidth="1"/>
     <col min="3" max="3" width="0.6640625" customWidth="1"/>
     <col min="4" max="4" width="1.1640625" customWidth="1"/>
-    <col min="5" max="5" width="41.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.83203125" customWidth="1"/>
-    <col min="7" max="8" width="4.1640625" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="2.1640625" customWidth="1"/>
+    <col min="6" max="6" width="2.83203125" customWidth="1"/>
+    <col min="7" max="7" width="2.1640625" customWidth="1"/>
+    <col min="8" max="8" width="1" customWidth="1"/>
+    <col min="9" max="9" width="1.33203125" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.6640625" customWidth="1"/>
+    <col min="20" max="20" width="1.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1496,10 +1525,10 @@
         <v>309</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>8</v>
+        <v>317</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>9</v>
+        <v>318</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>10</v>
@@ -1516,8 +1545,14 @@
       <c r="R1" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>42071</v>
       </c>
@@ -1551,11 +1586,16 @@
       <c r="K2" t="s">
         <v>310</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="M2" s="8"/>
+      <c r="S2" s="6" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="T2" s="6"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>45719</v>
       </c>
@@ -1589,9 +1629,6 @@
       <c r="K3" t="s">
         <v>314</v>
       </c>
-      <c r="L3" t="s">
-        <v>216</v>
-      </c>
       <c r="O3">
         <v>1898</v>
       </c>
@@ -1604,8 +1641,12 @@
       <c r="R3">
         <v>2074</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S3" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="T3" s="6"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>42387</v>
       </c>
@@ -1642,8 +1683,15 @@
       <c r="L4" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="M4" t="s">
+        <v>219</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="T4" s="6"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>45807</v>
       </c>
@@ -1678,7 +1726,10 @@
         <v>212</v>
       </c>
       <c r="L5" t="s">
-        <v>216</v>
+        <v>319</v>
+      </c>
+      <c r="M5" t="s">
+        <v>219</v>
       </c>
       <c r="O5">
         <v>246</v>
@@ -1692,8 +1743,12 @@
       <c r="R5">
         <v>259</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S5" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="T5" s="6"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>45782</v>
       </c>
@@ -1727,9 +1782,7 @@
       <c r="K6" t="s">
         <v>212</v>
       </c>
-      <c r="L6" t="s">
-        <v>216</v>
-      </c>
+      <c r="M6" s="7"/>
       <c r="O6">
         <v>739</v>
       </c>
@@ -1742,8 +1795,12 @@
       <c r="R6">
         <v>1190</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S6" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="T6" s="6"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>41992</v>
       </c>
@@ -1778,10 +1835,10 @@
         <v>212</v>
       </c>
       <c r="L7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N7" t="s">
         <v>224</v>
@@ -1798,8 +1855,14 @@
       <c r="R7">
         <v>157</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="T7" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>45800</v>
       </c>
@@ -1833,9 +1896,8 @@
       <c r="K8" t="s">
         <v>310</v>
       </c>
-      <c r="L8" t="s">
-        <v>216</v>
-      </c>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
       <c r="O8">
         <v>803</v>
       </c>
@@ -1848,8 +1910,12 @@
       <c r="R8">
         <v>883</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="T8" s="6"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>42072</v>
       </c>
@@ -1884,10 +1950,17 @@
         <v>212</v>
       </c>
       <c r="L9" t="s">
+        <v>219</v>
+      </c>
+      <c r="M9" t="s">
+        <v>219</v>
+      </c>
+      <c r="S9" s="6" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="T9" s="6"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>42071</v>
       </c>
@@ -1922,7 +1995,10 @@
         <v>314</v>
       </c>
       <c r="L10" t="s">
-        <v>218</v>
+        <v>219</v>
+      </c>
+      <c r="M10" t="s">
+        <v>219</v>
       </c>
       <c r="O10">
         <v>278</v>
@@ -1936,8 +2012,12 @@
       <c r="R10">
         <v>351</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="T10" s="6"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>42063</v>
       </c>
@@ -1974,6 +2054,9 @@
       <c r="L11" t="s">
         <v>219</v>
       </c>
+      <c r="M11" t="s">
+        <v>219</v>
+      </c>
       <c r="O11">
         <v>2</v>
       </c>
@@ -1986,8 +2069,12 @@
       <c r="R11">
         <v>65</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="T11" s="6"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>42068</v>
       </c>
@@ -2016,13 +2103,16 @@
         <v>213</v>
       </c>
       <c r="J12" t="s">
-        <v>214</v>
+        <v>316</v>
       </c>
       <c r="K12" t="s">
         <v>212</v>
       </c>
       <c r="L12" t="s">
-        <v>216</v>
+        <v>219</v>
+      </c>
+      <c r="M12" t="s">
+        <v>219</v>
       </c>
       <c r="O12">
         <v>145</v>
@@ -2036,8 +2126,11 @@
       <c r="R12">
         <v>275</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>45808</v>
       </c>
@@ -2072,7 +2165,10 @@
         <v>212</v>
       </c>
       <c r="L13" t="s">
-        <v>218</v>
+        <v>219</v>
+      </c>
+      <c r="M13" t="s">
+        <v>219</v>
       </c>
       <c r="O13">
         <v>348</v>
@@ -2086,8 +2182,11 @@
       <c r="R13">
         <v>391</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>45807</v>
       </c>
@@ -2122,7 +2221,10 @@
         <v>313</v>
       </c>
       <c r="L14" t="s">
-        <v>216</v>
+        <v>219</v>
+      </c>
+      <c r="M14" t="s">
+        <v>219</v>
       </c>
       <c r="O14">
         <v>54</v>
@@ -2136,8 +2238,11 @@
       <c r="R14">
         <v>248</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>45752</v>
       </c>
@@ -2171,9 +2276,7 @@
       <c r="K15" t="s">
         <v>314</v>
       </c>
-      <c r="L15" t="s">
-        <v>216</v>
-      </c>
+      <c r="M15" s="8"/>
       <c r="O15">
         <v>174</v>
       </c>
@@ -2186,8 +2289,11 @@
       <c r="R15">
         <v>212</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>45808</v>
       </c>
@@ -2222,16 +2328,22 @@
         <v>212</v>
       </c>
       <c r="L16" t="s">
-        <v>218</v>
+        <v>319</v>
       </c>
       <c r="M16" t="s">
-        <v>222</v>
+        <v>319</v>
       </c>
       <c r="N16" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S16" t="s">
+        <v>218</v>
+      </c>
+      <c r="T16" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>42067</v>
       </c>
@@ -2268,6 +2380,9 @@
       <c r="L17" t="s">
         <v>219</v>
       </c>
+      <c r="M17" t="s">
+        <v>219</v>
+      </c>
       <c r="O17">
         <v>265</v>
       </c>
@@ -2280,8 +2395,11 @@
       <c r="R17">
         <v>282</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S17" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>45795</v>
       </c>
@@ -2315,9 +2433,8 @@
       <c r="K18" t="s">
         <v>310</v>
       </c>
-      <c r="L18" t="s">
-        <v>216</v>
-      </c>
+      <c r="L18" s="7"/>
+      <c r="M18" s="8"/>
       <c r="O18">
         <v>309</v>
       </c>
@@ -2330,8 +2447,11 @@
       <c r="R18">
         <v>362</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>42059</v>
       </c>
@@ -2365,9 +2485,10 @@
       <c r="K19" t="s">
         <v>310</v>
       </c>
-      <c r="L19" t="s">
-        <v>218</v>
-      </c>
+      <c r="L19" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="M19" s="8"/>
       <c r="O19">
         <v>345</v>
       </c>
@@ -2380,8 +2501,11 @@
       <c r="R19">
         <v>618</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S19" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>45662</v>
       </c>
@@ -2416,9 +2540,6 @@
       <c r="K20" t="s">
         <v>313</v>
       </c>
-      <c r="L20" t="s">
-        <v>291</v>
-      </c>
       <c r="O20">
         <v>662</v>
       </c>
@@ -2431,8 +2552,11 @@
       <c r="R20">
         <v>835</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S20" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>41618</v>
       </c>
@@ -2467,8 +2591,9 @@
         <v>314</v>
       </c>
       <c r="L21" t="s">
-        <v>216</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="M21" s="8"/>
       <c r="O21">
         <v>1286</v>
       </c>
@@ -2481,8 +2606,11 @@
       <c r="R21">
         <v>1435</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S21" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>42067</v>
       </c>
@@ -2519,6 +2647,9 @@
       <c r="L22" t="s">
         <v>219</v>
       </c>
+      <c r="M22" t="s">
+        <v>219</v>
+      </c>
       <c r="O22">
         <v>60</v>
       </c>
@@ -2531,8 +2662,11 @@
       <c r="R22">
         <v>190</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S22" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>41181</v>
       </c>
@@ -2566,8 +2700,11 @@
       <c r="K23" t="s">
         <v>214</v>
       </c>
-      <c r="L23" t="s">
-        <v>216</v>
+      <c r="L23" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="O23">
         <v>397</v>
@@ -2581,8 +2718,11 @@
       <c r="R23">
         <v>533</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S23" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>40939</v>
       </c>
@@ -2617,7 +2757,10 @@
         <v>212</v>
       </c>
       <c r="L24" t="s">
-        <v>216</v>
+        <v>219</v>
+      </c>
+      <c r="M24" t="s">
+        <v>219</v>
       </c>
       <c r="O24">
         <v>81</v>
@@ -2631,8 +2774,11 @@
       <c r="R24">
         <v>189</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S24" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>45808</v>
       </c>
@@ -2667,7 +2813,10 @@
         <v>314</v>
       </c>
       <c r="L25" t="s">
-        <v>218</v>
+        <v>319</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="O25">
         <v>223</v>
@@ -2681,8 +2830,11 @@
       <c r="R25">
         <v>316</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S25" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>45409</v>
       </c>
@@ -2716,9 +2868,7 @@
       <c r="K26" t="s">
         <v>314</v>
       </c>
-      <c r="L26" t="s">
-        <v>218</v>
-      </c>
+      <c r="M26" s="7"/>
       <c r="O26">
         <v>9382</v>
       </c>
@@ -2731,8 +2881,11 @@
       <c r="R26">
         <v>9478</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S26" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>42065</v>
       </c>
@@ -2767,7 +2920,10 @@
         <v>314</v>
       </c>
       <c r="L27" t="s">
-        <v>216</v>
+        <v>219</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="O27">
         <v>412</v>
@@ -2781,8 +2937,11 @@
       <c r="R27">
         <v>528</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S27" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>45384</v>
       </c>
@@ -2816,9 +2975,8 @@
       <c r="K28" t="s">
         <v>310</v>
       </c>
-      <c r="L28" t="s">
-        <v>216</v>
-      </c>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
       <c r="O28">
         <v>5010</v>
       </c>
@@ -2831,8 +2989,11 @@
       <c r="R28">
         <v>5059</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S28" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>45660</v>
       </c>
@@ -2866,9 +3027,7 @@
       <c r="K29" t="s">
         <v>212</v>
       </c>
-      <c r="L29" t="s">
-        <v>216</v>
-      </c>
+      <c r="M29" s="7"/>
       <c r="O29">
         <v>193</v>
       </c>
@@ -2881,8 +3040,11 @@
       <c r="R29">
         <v>384</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S29" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>45808</v>
       </c>
@@ -2917,13 +3079,19 @@
         <v>213</v>
       </c>
       <c r="L30" t="s">
-        <v>218</v>
+        <v>319</v>
+      </c>
+      <c r="M30" t="s">
+        <v>319</v>
       </c>
       <c r="N30" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S30" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>44642</v>
       </c>
@@ -2957,9 +3125,7 @@
       <c r="K31" t="s">
         <v>314</v>
       </c>
-      <c r="L31" t="s">
-        <v>216</v>
-      </c>
+      <c r="M31" s="8"/>
       <c r="O31">
         <v>5609</v>
       </c>
@@ -2972,8 +3138,11 @@
       <c r="R31">
         <v>5657</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S31" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>45691</v>
       </c>
@@ -3008,9 +3177,7 @@
       <c r="K32" t="s">
         <v>314</v>
       </c>
-      <c r="L32" t="s">
-        <v>291</v>
-      </c>
+      <c r="M32" s="8"/>
       <c r="O32">
         <v>622</v>
       </c>
@@ -3023,8 +3190,11 @@
       <c r="R32">
         <v>714</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S32" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>45660</v>
       </c>
@@ -3059,7 +3229,10 @@
         <v>255</v>
       </c>
       <c r="L33" t="s">
-        <v>256</v>
+        <v>219</v>
+      </c>
+      <c r="M33" t="s">
+        <v>219</v>
       </c>
       <c r="O33">
         <v>662</v>
@@ -3073,8 +3246,11 @@
       <c r="R33">
         <v>835</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S33" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>44345</v>
       </c>
@@ -3109,7 +3285,10 @@
         <v>314</v>
       </c>
       <c r="L34" t="s">
-        <v>216</v>
+        <v>219</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="O34">
         <v>2087</v>
@@ -3123,8 +3302,11 @@
       <c r="R34">
         <v>2283</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S34" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>42068</v>
       </c>
@@ -3158,7 +3340,10 @@
       <c r="K35" t="s">
         <v>310</v>
       </c>
-      <c r="L35" t="s">
+      <c r="L35" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="M35" s="7" t="s">
         <v>219</v>
       </c>
       <c r="O35">
@@ -3173,8 +3358,11 @@
       <c r="R35">
         <v>774</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S35" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>45384</v>
       </c>
@@ -3208,9 +3396,7 @@
       <c r="K36" t="s">
         <v>212</v>
       </c>
-      <c r="L36" t="s">
-        <v>218</v>
-      </c>
+      <c r="M36" s="7"/>
       <c r="O36">
         <v>327</v>
       </c>
@@ -3223,8 +3409,11 @@
       <c r="R36">
         <v>381</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S36" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>45791</v>
       </c>
@@ -3258,9 +3447,7 @@
       <c r="K37" t="s">
         <v>212</v>
       </c>
-      <c r="L37" t="s">
-        <v>219</v>
-      </c>
+      <c r="M37" s="7"/>
       <c r="O37">
         <v>95</v>
       </c>
@@ -3273,8 +3460,11 @@
       <c r="R37">
         <v>139</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S37" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>45707</v>
       </c>
@@ -3308,9 +3498,7 @@
       <c r="K38" t="s">
         <v>212</v>
       </c>
-      <c r="L38" t="s">
-        <v>256</v>
-      </c>
+      <c r="M38" s="8"/>
       <c r="O38">
         <v>617</v>
       </c>
@@ -3323,8 +3511,11 @@
       <c r="R38">
         <v>791</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S38" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>44680</v>
       </c>
@@ -3358,9 +3549,6 @@
       <c r="K39" t="s">
         <v>212</v>
       </c>
-      <c r="L39" t="s">
-        <v>219</v>
-      </c>
       <c r="O39">
         <v>387</v>
       </c>
@@ -3373,8 +3561,11 @@
       <c r="R39">
         <v>444</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S39" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>43757</v>
       </c>
@@ -3409,10 +3600,16 @@
         <v>212</v>
       </c>
       <c r="L40" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="S40" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>42059</v>
       </c>
@@ -3441,13 +3638,16 @@
         <v>255</v>
       </c>
       <c r="J41" t="s">
-        <v>214</v>
+        <v>316</v>
       </c>
       <c r="K41" t="s">
         <v>214</v>
       </c>
-      <c r="L41" t="s">
-        <v>218</v>
+      <c r="L41" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="O41">
         <v>167</v>
@@ -3461,8 +3661,11 @@
       <c r="R41">
         <v>391</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S41" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>45384</v>
       </c>
@@ -3496,9 +3699,8 @@
       <c r="K42" t="s">
         <v>310</v>
       </c>
-      <c r="L42" t="s">
-        <v>216</v>
-      </c>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7"/>
       <c r="O42">
         <v>5010</v>
       </c>
@@ -3511,8 +3713,11 @@
       <c r="R42">
         <v>5060</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S42" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>40939</v>
       </c>
@@ -3547,8 +3752,9 @@
         <v>314</v>
       </c>
       <c r="L43" t="s">
-        <v>216</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="M43" s="8"/>
       <c r="O43">
         <v>316</v>
       </c>
@@ -3561,8 +3767,11 @@
       <c r="R43">
         <v>373</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S43" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>42069</v>
       </c>
@@ -3597,10 +3806,14 @@
         <v>212</v>
       </c>
       <c r="L44" t="s">
+        <v>219</v>
+      </c>
+      <c r="M44" s="8"/>
+      <c r="S44" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>45741</v>
       </c>
@@ -3634,9 +3847,6 @@
       <c r="K45" t="s">
         <v>212</v>
       </c>
-      <c r="L45" t="s">
-        <v>216</v>
-      </c>
       <c r="O45">
         <v>278</v>
       </c>
@@ -3649,8 +3859,11 @@
       <c r="R45">
         <v>345</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S45" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>44660</v>
       </c>
@@ -3684,9 +3897,8 @@
       <c r="K46" t="s">
         <v>310</v>
       </c>
-      <c r="L46" t="s">
-        <v>216</v>
-      </c>
+      <c r="L46" s="7"/>
+      <c r="M46" s="8"/>
       <c r="O46">
         <v>2648</v>
       </c>
@@ -3699,8 +3911,11 @@
       <c r="R46">
         <v>2746</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S46" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>42071</v>
       </c>
@@ -3735,8 +3950,9 @@
         <v>314</v>
       </c>
       <c r="L47" t="s">
-        <v>216</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="M47" s="8"/>
       <c r="O47">
         <v>1287</v>
       </c>
@@ -3749,8 +3965,11 @@
       <c r="R47">
         <v>1342</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S47" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>45801</v>
       </c>
@@ -3785,9 +4004,7 @@
       <c r="K48" t="s">
         <v>314</v>
       </c>
-      <c r="L48" t="s">
-        <v>219</v>
-      </c>
+      <c r="M48" s="8"/>
       <c r="O48">
         <v>354</v>
       </c>
@@ -3800,8 +4017,11 @@
       <c r="R48">
         <v>450</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S48" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>44641</v>
       </c>
@@ -3835,9 +4055,7 @@
       <c r="K49" t="s">
         <v>314</v>
       </c>
-      <c r="L49" t="s">
-        <v>220</v>
-      </c>
+      <c r="M49" s="8"/>
       <c r="O49">
         <v>320</v>
       </c>
@@ -3850,8 +4068,11 @@
       <c r="R49">
         <v>590</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S49" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>45808</v>
       </c>
@@ -3885,11 +4106,17 @@
       <c r="K50" t="s">
         <v>310</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L50" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="M50" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="S50" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>42069</v>
       </c>
@@ -3924,7 +4151,10 @@
         <v>314</v>
       </c>
       <c r="L51" t="s">
-        <v>216</v>
+        <v>219</v>
+      </c>
+      <c r="M51" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="O51">
         <v>512</v>
@@ -3938,8 +4168,11 @@
       <c r="R51">
         <v>666</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S51" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>45810</v>
       </c>
@@ -3974,10 +4207,10 @@
         <v>212</v>
       </c>
       <c r="L52" t="s">
-        <v>217</v>
+        <v>319</v>
       </c>
       <c r="M52" t="s">
-        <v>223</v>
+        <v>319</v>
       </c>
       <c r="O52">
         <v>660</v>
@@ -3991,8 +4224,14 @@
       <c r="R52">
         <v>703</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S52" t="s">
+        <v>217</v>
+      </c>
+      <c r="T52" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>44617</v>
       </c>
@@ -4021,14 +4260,12 @@
         <v>214</v>
       </c>
       <c r="J53" t="s">
-        <v>214</v>
+        <v>316</v>
       </c>
       <c r="K53" t="s">
         <v>212</v>
       </c>
-      <c r="L53" t="s">
-        <v>219</v>
-      </c>
+      <c r="M53" s="7"/>
       <c r="O53">
         <v>314</v>
       </c>
@@ -4041,8 +4278,11 @@
       <c r="R53">
         <v>353</v>
       </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S53" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>45800</v>
       </c>
@@ -4076,9 +4316,8 @@
       <c r="K54" t="s">
         <v>310</v>
       </c>
-      <c r="L54" t="s">
-        <v>256</v>
-      </c>
+      <c r="L54" s="7"/>
+      <c r="M54" s="7"/>
       <c r="O54">
         <v>670</v>
       </c>
@@ -4091,8 +4330,11 @@
       <c r="R54">
         <v>812</v>
       </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S54" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>42059</v>
       </c>
@@ -4127,8 +4369,9 @@
         <v>314</v>
       </c>
       <c r="L55" t="s">
-        <v>218</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="M55" s="8"/>
       <c r="O55">
         <v>326</v>
       </c>
@@ -4141,8 +4384,11 @@
       <c r="R55">
         <v>329</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S55" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>45805</v>
       </c>
@@ -4177,7 +4423,10 @@
         <v>213</v>
       </c>
       <c r="L56" t="s">
-        <v>216</v>
+        <v>219</v>
+      </c>
+      <c r="M56" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="O56">
         <v>309</v>
@@ -4191,8 +4440,11 @@
       <c r="R56">
         <v>362</v>
       </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S56" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>42071</v>
       </c>
@@ -4221,13 +4473,16 @@
         <v>214</v>
       </c>
       <c r="J57" t="s">
-        <v>214</v>
+        <v>316</v>
       </c>
       <c r="K57" t="s">
         <v>214</v>
       </c>
-      <c r="L57" t="s">
-        <v>216</v>
+      <c r="L57" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="M57" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="O57">
         <v>561</v>
@@ -4241,8 +4496,11 @@
       <c r="R57">
         <v>676</v>
       </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S57" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>42063</v>
       </c>
@@ -4277,7 +4535,10 @@
         <v>213</v>
       </c>
       <c r="L58" t="s">
-        <v>220</v>
+        <v>219</v>
+      </c>
+      <c r="M58" t="s">
+        <v>219</v>
       </c>
       <c r="O58">
         <v>1</v>
@@ -4291,8 +4552,11 @@
       <c r="R58">
         <v>128</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S58" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>42068</v>
       </c>
@@ -4321,16 +4585,22 @@
         <v>213</v>
       </c>
       <c r="J59" t="s">
-        <v>214</v>
+        <v>316</v>
       </c>
       <c r="K59" t="s">
         <v>213</v>
       </c>
       <c r="L59" t="s">
+        <v>219</v>
+      </c>
+      <c r="M59" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="S59" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>45754</v>
       </c>
@@ -4364,9 +4634,7 @@
       <c r="K60" t="s">
         <v>314</v>
       </c>
-      <c r="L60" t="s">
-        <v>216</v>
-      </c>
+      <c r="M60" s="8"/>
       <c r="O60">
         <v>787</v>
       </c>
@@ -4379,8 +4647,11 @@
       <c r="R60">
         <v>962</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S60" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>45384</v>
       </c>
@@ -4414,9 +4685,6 @@
       <c r="K61" t="s">
         <v>314</v>
       </c>
-      <c r="L61" t="s">
-        <v>216</v>
-      </c>
       <c r="O61">
         <v>5010</v>
       </c>
@@ -4429,8 +4697,11 @@
       <c r="R61">
         <v>5058</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S61" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>45384</v>
       </c>
@@ -4464,9 +4735,7 @@
       <c r="K62" t="s">
         <v>310</v>
       </c>
-      <c r="L62" t="s">
-        <v>216</v>
-      </c>
+      <c r="L62" s="7"/>
       <c r="O62">
         <v>5010</v>
       </c>
@@ -4479,8 +4748,11 @@
       <c r="R62">
         <v>5061</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S62" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>45809</v>
       </c>
@@ -4515,7 +4787,10 @@
         <v>314</v>
       </c>
       <c r="L63" t="s">
-        <v>216</v>
+        <v>219</v>
+      </c>
+      <c r="M63" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="O63">
         <v>6332</v>
@@ -4529,8 +4804,11 @@
       <c r="R63">
         <v>6553</v>
       </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S63" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>42065</v>
       </c>
@@ -4564,11 +4842,15 @@
       <c r="K64" t="s">
         <v>310</v>
       </c>
-      <c r="L64" t="s">
+      <c r="L64" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="M64" s="8"/>
+      <c r="S64" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>45733</v>
       </c>
@@ -4602,9 +4884,7 @@
       <c r="K65" t="s">
         <v>314</v>
       </c>
-      <c r="L65" t="s">
-        <v>216</v>
-      </c>
+      <c r="M65" s="8"/>
       <c r="O65">
         <v>1166</v>
       </c>
@@ -4617,8 +4897,11 @@
       <c r="R65">
         <v>1631</v>
       </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S65" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>45714</v>
       </c>
@@ -4652,9 +4935,7 @@
       <c r="K66" t="s">
         <v>314</v>
       </c>
-      <c r="L66" t="s">
-        <v>216</v>
-      </c>
+      <c r="M66" s="8"/>
       <c r="O66">
         <v>2991</v>
       </c>
@@ -4667,8 +4948,11 @@
       <c r="R66">
         <v>3134</v>
       </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S66" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>45384</v>
       </c>
@@ -4702,9 +4986,6 @@
       <c r="K67" t="s">
         <v>212</v>
       </c>
-      <c r="L67" t="s">
-        <v>218</v>
-      </c>
       <c r="O67">
         <v>255</v>
       </c>
@@ -4717,8 +4998,11 @@
       <c r="R67">
         <v>303</v>
       </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S67" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>45384</v>
       </c>
@@ -4752,9 +5036,6 @@
       <c r="K68" t="s">
         <v>314</v>
       </c>
-      <c r="L68" t="s">
-        <v>218</v>
-      </c>
       <c r="O68">
         <v>8783</v>
       </c>
@@ -4767,8 +5048,11 @@
       <c r="R68">
         <v>8890</v>
       </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S68" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>45690</v>
       </c>
@@ -4802,9 +5086,7 @@
       <c r="K69" t="s">
         <v>212</v>
       </c>
-      <c r="L69" t="s">
-        <v>220</v>
-      </c>
+      <c r="M69" s="8"/>
       <c r="O69">
         <v>717</v>
       </c>
@@ -4817,8 +5099,11 @@
       <c r="R69">
         <v>767</v>
       </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S69" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>45658</v>
       </c>
@@ -4853,9 +5138,8 @@
       <c r="K70" t="s">
         <v>214</v>
       </c>
-      <c r="L70" t="s">
-        <v>291</v>
-      </c>
+      <c r="L70" s="7"/>
+      <c r="M70" s="7"/>
       <c r="O70">
         <v>58</v>
       </c>
@@ -4868,8 +5152,11 @@
       <c r="R70">
         <v>167</v>
       </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S70" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" s="5">
         <v>45674</v>
       </c>
@@ -4903,9 +5190,6 @@
       <c r="K71" t="s">
         <v>314</v>
       </c>
-      <c r="L71" t="s">
-        <v>219</v>
-      </c>
       <c r="O71">
         <v>149</v>
       </c>
@@ -4918,8 +5202,11 @@
       <c r="R71">
         <v>199</v>
       </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S71" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>43757</v>
       </c>
@@ -4956,6 +5243,7 @@
       <c r="L72" t="s">
         <v>219</v>
       </c>
+      <c r="M72" s="8"/>
       <c r="O72">
         <v>919</v>
       </c>
@@ -4968,8 +5256,11 @@
       <c r="R72">
         <v>961</v>
       </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S72" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>45389</v>
       </c>
@@ -5003,9 +5294,7 @@
       <c r="K73" t="s">
         <v>314</v>
       </c>
-      <c r="L73" t="s">
-        <v>220</v>
-      </c>
+      <c r="M73" s="8"/>
       <c r="O73">
         <v>270</v>
       </c>
@@ -5018,8 +5307,11 @@
       <c r="R73">
         <v>324</v>
       </c>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S73" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>45383</v>
       </c>
@@ -5053,9 +5345,7 @@
       <c r="K74" t="s">
         <v>314</v>
       </c>
-      <c r="L74" t="s">
-        <v>218</v>
-      </c>
+      <c r="M74" s="8"/>
       <c r="O74">
         <v>9367</v>
       </c>
@@ -5068,8 +5358,11 @@
       <c r="R74">
         <v>9455</v>
       </c>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S74" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>45204</v>
       </c>
@@ -5104,10 +5397,14 @@
         <v>213</v>
       </c>
       <c r="L75" t="s">
+        <v>219</v>
+      </c>
+      <c r="M75" s="8"/>
+      <c r="S75" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>45378</v>
       </c>
@@ -5141,9 +5438,7 @@
       <c r="K76" t="s">
         <v>212</v>
       </c>
-      <c r="L76" t="s">
-        <v>220</v>
-      </c>
+      <c r="M76" s="8"/>
       <c r="O76">
         <v>145</v>
       </c>
@@ -5155,6 +5450,9 @@
       </c>
       <c r="R76">
         <v>395</v>
+      </c>
+      <c r="S76" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
